--- a/salidas/empresas/MU.xlsx
+++ b/salidas/empresas/MU.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>14.31501483917236</v>
+        <v>14.31501293182373</v>
       </c>
       <c r="C2" t="n">
         <v>14.68000030517578</v>
@@ -501,7 +513,7 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>14.35401725769043</v>
+        <v>14.3540210723877</v>
       </c>
       <c r="C4" t="n">
         <v>14.72000026702881</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>16.54807472229004</v>
+        <v>16.5480785369873</v>
       </c>
       <c r="C5" t="n">
         <v>16.96999931335449</v>
@@ -558,7 +570,7 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>14.68556690216064</v>
+        <v>14.6855640411377</v>
       </c>
       <c r="C7" t="n">
         <v>15.0600004196167</v>
@@ -596,7 +608,7 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>16.85037231445312</v>
+        <v>16.85037422180176</v>
       </c>
       <c r="C9" t="n">
         <v>17.28000068664551</v>
@@ -634,7 +646,7 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
@@ -653,7 +665,7 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>14.23700141906738</v>
+        <v>14.23700332641602</v>
       </c>
       <c r="C12" t="n">
         <v>14.60000038146973</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>13.61291599273682</v>
+        <v>13.61291408538818</v>
       </c>
       <c r="C13" t="n">
         <v>13.96000003814697</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>12.62802410125732</v>
+        <v>12.62802600860596</v>
       </c>
       <c r="C14" t="n">
         <v>12.94999980926514</v>
@@ -729,7 +741,7 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>11.7796573638916</v>
+        <v>11.77965641021729</v>
       </c>
       <c r="C16" t="n">
         <v>12.07999992370605</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>11.18482208251953</v>
+        <v>11.18482398986816</v>
       </c>
       <c r="C17" t="n">
         <v>11.47000026702881</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>11.87717056274414</v>
+        <v>11.87717151641846</v>
       </c>
       <c r="C18" t="n">
         <v>12.18000030517578</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>12.21847057342529</v>
+        <v>12.21846866607666</v>
       </c>
       <c r="C19" t="n">
         <v>12.52999973297119</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>11.57487678527832</v>
+        <v>11.57487773895264</v>
       </c>
       <c r="C20" t="n">
         <v>11.86999988555908</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>11.16532039642334</v>
+        <v>11.16532135009766</v>
       </c>
       <c r="C21" t="n">
         <v>11.44999980926514</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>10.82402229309082</v>
+        <v>10.82402515411377</v>
       </c>
       <c r="C22" t="n">
         <v>11.10000038146973</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>10.24869155883789</v>
+        <v>10.24869251251221</v>
       </c>
       <c r="C23" t="n">
         <v>10.51000022888184</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>8.113142013549805</v>
+        <v>8.113141059875488</v>
       </c>
       <c r="C24" t="n">
         <v>8.319999694824219</v>
@@ -919,7 +931,7 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>6.816208839416504</v>
+        <v>6.816208362579346</v>
       </c>
       <c r="C26" t="n">
         <v>6.989999771118164</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>7.333032131195068</v>
+        <v>7.333031177520752</v>
       </c>
       <c r="C27" t="n">
         <v>7.519999980926514</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>5.821568965911865</v>
+        <v>5.821567535400391</v>
       </c>
       <c r="C28" t="n">
         <v>5.96999979019165</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>7.528059005737305</v>
+        <v>7.528058528900146</v>
       </c>
       <c r="C29" t="n">
         <v>7.71999979019165</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>7.869356155395508</v>
+        <v>7.869357109069824</v>
       </c>
       <c r="C30" t="n">
         <v>8.069999694824219</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>5.850823879241943</v>
+        <v>5.850822925567627</v>
       </c>
       <c r="C31" t="n">
         <v>6</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>4.709912300109863</v>
+        <v>4.70991325378418</v>
       </c>
       <c r="C32" t="n">
         <v>4.829999923706055</v>
@@ -1071,7 +1083,7 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>3.949305534362793</v>
+        <v>3.949306011199951</v>
       </c>
       <c r="C34" t="n">
         <v>4.050000190734863</v>
@@ -1109,7 +1121,7 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>2.671875476837158</v>
+        <v>2.671876192092896</v>
       </c>
       <c r="C36" t="n">
         <v>2.740000009536743</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>2.57436203956604</v>
+        <v>2.574361801147461</v>
       </c>
       <c r="C37" t="n">
         <v>2.640000104904175</v>
@@ -1166,7 +1178,7 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>3.139941215515137</v>
+        <v>3.139941930770874</v>
       </c>
       <c r="C39" t="n">
         <v>3.220000028610229</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>3.959056377410889</v>
+        <v>3.95905613899231</v>
       </c>
       <c r="C40" t="n">
         <v>4.059999942779541</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>4.758669376373291</v>
+        <v>4.758670330047607</v>
       </c>
       <c r="C41" t="n">
         <v>4.880000114440918</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>4.934192657470703</v>
+        <v>4.934194087982178</v>
       </c>
       <c r="C42" t="n">
         <v>5.059999942779541</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>4.934192657470703</v>
+        <v>4.934194087982178</v>
       </c>
       <c r="C43" t="n">
         <v>5.059999942779541</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>6.231125831604004</v>
+        <v>6.23112678527832</v>
       </c>
       <c r="C44" t="n">
         <v>6.389999866485596</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>7.186759948730469</v>
+        <v>7.186760425567627</v>
       </c>
       <c r="C45" t="n">
         <v>7.369999885559082</v>
@@ -1318,11 +1330,11 @@
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>7.996123313903809</v>
+        <v>7.996125221252441</v>
       </c>
       <c r="C46" t="n">
         <v>8.199999809265137</v>
@@ -1337,11 +1349,11 @@
       <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>6.621181011199951</v>
+        <v>6.621181964874268</v>
       </c>
       <c r="C47" t="n">
         <v>6.789999961853027</v>
@@ -1356,11 +1368,11 @@
       <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>7.333032131195068</v>
+        <v>7.333031177520752</v>
       </c>
       <c r="C48" t="n">
         <v>7.519999980926514</v>
@@ -1375,11 +1387,11 @@
       <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>10.29744815826416</v>
+        <v>10.29744720458984</v>
       </c>
       <c r="C49" t="n">
         <v>10.5600004196167</v>
@@ -1394,11 +1406,11 @@
       <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>8.50319766998291</v>
+        <v>8.503196716308594</v>
       </c>
       <c r="C50" t="n">
         <v>8.720000267028809</v>
@@ -1419,11 +1431,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>8.834743499755859</v>
+        <v>8.834742546081543</v>
       </c>
       <c r="C51" t="n">
         <v>9.060000419616699</v>
@@ -1444,11 +1456,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>10.11217308044434</v>
+        <v>10.11217403411865</v>
       </c>
       <c r="C52" t="n">
         <v>10.36999988555908</v>
@@ -1469,11 +1481,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>9.117531776428223</v>
+        <v>9.117530822753906</v>
       </c>
       <c r="C53" t="n">
         <v>9.350000381469727</v>
@@ -1494,11 +1506,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>8.863995552062988</v>
+        <v>8.863997459411621</v>
       </c>
       <c r="C54" t="n">
         <v>9.090000152587891</v>
@@ -1519,11 +1531,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>8.278916358947754</v>
+        <v>8.278914451599121</v>
       </c>
       <c r="C55" t="n">
         <v>8.489999771118164</v>
@@ -1544,11 +1556,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>7.0989990234375</v>
+        <v>7.098998546600342</v>
       </c>
       <c r="C56" t="n">
         <v>7.28000020980835</v>
@@ -1569,11 +1581,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>6.299385070800781</v>
+        <v>6.299386024475098</v>
       </c>
       <c r="C57" t="n">
         <v>6.460000038146973</v>
@@ -1588,11 +1600,11 @@
       <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>7.030739784240723</v>
+        <v>7.030739307403564</v>
       </c>
       <c r="C58" t="n">
         <v>7.210000038146973</v>
@@ -1607,7 +1619,7 @@
       <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
@@ -1626,11 +1638,11 @@
       <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>7.089247226715088</v>
+        <v>7.089247703552246</v>
       </c>
       <c r="C60" t="n">
         <v>7.269999980926514</v>
@@ -1645,7 +1657,7 @@
       <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
@@ -1664,7 +1676,7 @@
       <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
@@ -1689,11 +1701,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>10.85327816009521</v>
+        <v>10.8532772064209</v>
       </c>
       <c r="C63" t="n">
         <v>11.13000011444092</v>
@@ -1714,11 +1726,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>11.18482208251953</v>
+        <v>11.18482398986816</v>
       </c>
       <c r="C64" t="n">
         <v>11.47000026702881</v>
@@ -1739,11 +1751,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>11.03854942321777</v>
+        <v>11.03855323791504</v>
       </c>
       <c r="C65" t="n">
         <v>11.31999969482422</v>
@@ -1764,11 +1776,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>9.946398735046387</v>
+        <v>9.946399688720703</v>
       </c>
       <c r="C66" t="n">
         <v>10.19999980926514</v>
@@ -1789,7 +1801,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
@@ -1814,11 +1826,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>7.186759948730469</v>
+        <v>7.186760425567627</v>
       </c>
       <c r="C68" t="n">
         <v>7.369999885559082</v>
@@ -1839,11 +1851,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>5.763061046600342</v>
+        <v>5.763060569763184</v>
       </c>
       <c r="C69" t="n">
         <v>5.909999847412109</v>
@@ -1864,11 +1876,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>4.91469144821167</v>
+        <v>4.914690971374512</v>
       </c>
       <c r="C70" t="n">
         <v>5.039999961853027</v>
@@ -1889,11 +1901,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>5.451018333435059</v>
+        <v>5.451017379760742</v>
       </c>
       <c r="C71" t="n">
         <v>5.590000152587891</v>
@@ -1918,7 +1930,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
@@ -1947,11 +1959,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>6.133612155914307</v>
+        <v>6.133612632751465</v>
       </c>
       <c r="C73" t="n">
         <v>6.289999961853027</v>
@@ -1976,11 +1988,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>7.411043643951416</v>
+        <v>7.4110426902771</v>
       </c>
       <c r="C74" t="n">
         <v>7.599999904632568</v>
@@ -2003,11 +2015,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>8.337425231933594</v>
+        <v>8.337423324584961</v>
       </c>
       <c r="C75" t="n">
         <v>8.550000190734863</v>
@@ -2030,11 +2042,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>7.898611068725586</v>
+        <v>7.898612022399902</v>
       </c>
       <c r="C76" t="n">
         <v>8.100000381469727</v>
@@ -2057,11 +2069,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>6.426153659820557</v>
+        <v>6.426154136657715</v>
       </c>
       <c r="C77" t="n">
         <v>6.590000152587891</v>
@@ -2084,7 +2096,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
@@ -2111,7 +2123,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
@@ -2138,11 +2150,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>6.055601119995117</v>
+        <v>6.055602073669434</v>
       </c>
       <c r="C80" t="n">
         <v>6.210000038146973</v>
@@ -2165,11 +2177,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>6.055601119995117</v>
+        <v>6.055602073669434</v>
       </c>
       <c r="C81" t="n">
         <v>6.210000038146973</v>
@@ -2192,11 +2204,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>5.831319808959961</v>
+        <v>5.831320762634277</v>
       </c>
       <c r="C82" t="n">
         <v>5.980000019073486</v>
@@ -2219,11 +2231,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>5.294995784759521</v>
+        <v>5.294994831085205</v>
       </c>
       <c r="C83" t="n">
         <v>5.429999828338623</v>
@@ -2246,11 +2258,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>5.821568965911865</v>
+        <v>5.821567535400391</v>
       </c>
       <c r="C84" t="n">
         <v>5.96999979019165</v>
@@ -2273,11 +2285,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>6.182370185852051</v>
+        <v>6.182369232177734</v>
       </c>
       <c r="C85" t="n">
         <v>6.340000152587891</v>
@@ -2300,7 +2312,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
@@ -2327,11 +2339,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>8.171648979187012</v>
+        <v>8.171650886535645</v>
       </c>
       <c r="C87" t="n">
         <v>8.380000114440918</v>
@@ -2354,11 +2366,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>9.731866836547852</v>
+        <v>9.731864929199219</v>
       </c>
       <c r="C88" t="n">
         <v>9.979999542236328</v>
@@ -2381,7 +2393,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
@@ -2408,7 +2420,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
@@ -2435,11 +2447,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>13.97371578216553</v>
+        <v>13.97371482849121</v>
       </c>
       <c r="C91" t="n">
         <v>14.32999992370605</v>
@@ -2462,11 +2474,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>12.91081714630127</v>
+        <v>12.910813331604</v>
       </c>
       <c r="C92" t="n">
         <v>13.23999977111816</v>
@@ -2489,11 +2501,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>13.23261260986328</v>
+        <v>13.23261070251465</v>
       </c>
       <c r="C93" t="n">
         <v>13.56999969482422</v>
@@ -2516,11 +2528,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>17.03564453125</v>
+        <v>17.03564262390137</v>
       </c>
       <c r="C94" t="n">
         <v>17.46999931335449</v>
@@ -2543,11 +2555,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>17.24042320251465</v>
+        <v>17.24042510986328</v>
       </c>
       <c r="C95" t="n">
         <v>17.68000030517578</v>
@@ -2572,7 +2584,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
@@ -2601,11 +2613,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>21.2092342376709</v>
+        <v>21.20923233032227</v>
       </c>
       <c r="C97" t="n">
         <v>21.75</v>
@@ -2630,11 +2642,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>22.4671573638916</v>
+        <v>22.46716117858887</v>
       </c>
       <c r="C98" t="n">
         <v>23.04000091552734</v>
@@ -2659,7 +2671,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
@@ -2688,7 +2700,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
@@ -2717,7 +2729,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
@@ -2746,7 +2758,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
@@ -2775,11 +2787,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>32.13076782226562</v>
+        <v>32.13077163696289</v>
       </c>
       <c r="C103" t="n">
         <v>32.95000076293945</v>
@@ -2804,11 +2816,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>29.79044342041016</v>
+        <v>29.79043960571289</v>
       </c>
       <c r="C104" t="n">
         <v>30.54999923706055</v>
@@ -2833,11 +2845,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>31.78947257995605</v>
+        <v>31.78946685791016</v>
       </c>
       <c r="C105" t="n">
         <v>32.59999847412109</v>
@@ -2862,11 +2874,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>33.40819549560547</v>
+        <v>33.40820693969727</v>
       </c>
       <c r="C106" t="n">
         <v>34.2599983215332</v>
@@ -2891,11 +2903,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>32.26728820800781</v>
+        <v>32.26729202270508</v>
       </c>
       <c r="C107" t="n">
         <v>33.09000015258789</v>
@@ -2920,7 +2932,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
@@ -2949,7 +2961,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
@@ -2978,11 +2990,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>28.54226493835449</v>
+        <v>28.54226684570312</v>
       </c>
       <c r="C110" t="n">
         <v>29.27000045776367</v>
@@ -3007,11 +3019,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>29.90745544433594</v>
+        <v>29.90745735168457</v>
       </c>
       <c r="C111" t="n">
         <v>30.67000007629395</v>
@@ -3036,11 +3048,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>26.45546913146973</v>
+        <v>26.45546722412109</v>
       </c>
       <c r="C112" t="n">
         <v>27.1299991607666</v>
@@ -3065,11 +3077,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>27.43060684204102</v>
+        <v>27.43060493469238</v>
       </c>
       <c r="C113" t="n">
         <v>28.1299991607666</v>
@@ -3094,11 +3106,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>27.23558616638184</v>
+        <v>27.2355842590332</v>
       </c>
       <c r="C114" t="n">
         <v>27.93000030517578</v>
@@ -3123,7 +3135,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
@@ -3152,7 +3164,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
@@ -3181,11 +3193,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>16.00199508666992</v>
+        <v>16.00200080871582</v>
       </c>
       <c r="C117" t="n">
         <v>16.40999984741211</v>
@@ -3210,7 +3222,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
@@ -3239,7 +3251,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
@@ -3268,11 +3280,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>15.533935546875</v>
+        <v>15.53393459320068</v>
       </c>
       <c r="C120" t="n">
         <v>15.93000030517578</v>
@@ -3297,11 +3309,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>13.80794239044189</v>
+        <v>13.80794334411621</v>
       </c>
       <c r="C121" t="n">
         <v>14.15999984741211</v>
@@ -3326,7 +3338,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
@@ -3355,11 +3367,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>10.36570835113525</v>
+        <v>10.36570739746094</v>
       </c>
       <c r="C123" t="n">
         <v>10.63000011444092</v>
@@ -3384,11 +3396,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>10.20968627929688</v>
+        <v>10.20968818664551</v>
       </c>
       <c r="C124" t="n">
         <v>10.47000026702881</v>
@@ -3413,7 +3425,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
@@ -3442,11 +3454,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>12.40374374389648</v>
+        <v>12.4037446975708</v>
       </c>
       <c r="C126" t="n">
         <v>12.72000026702881</v>
@@ -3471,11 +3483,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>13.41788864135742</v>
+        <v>13.41788959503174</v>
       </c>
       <c r="C127" t="n">
         <v>13.76000022888184</v>
@@ -3500,7 +3512,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
@@ -3529,11 +3541,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>16.08001518249512</v>
+        <v>16.08000946044922</v>
       </c>
       <c r="C129" t="n">
         <v>16.48999977111816</v>
@@ -3558,11 +3570,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>17.33793830871582</v>
+        <v>17.33794212341309</v>
       </c>
       <c r="C130" t="n">
         <v>17.78000068664551</v>
@@ -3587,11 +3599,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>16.73335266113281</v>
+        <v>16.73335456848145</v>
       </c>
       <c r="C131" t="n">
         <v>17.15999984741211</v>
@@ -3614,11 +3626,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>19.0444278717041</v>
+        <v>19.04442977905273</v>
       </c>
       <c r="C132" t="n">
         <v>19.53000068664551</v>
@@ -3641,11 +3653,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>21.37500381469727</v>
+        <v>21.37500953674316</v>
       </c>
       <c r="C133" t="n">
         <v>21.92000007629395</v>
@@ -3668,11 +3680,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>23.51056098937988</v>
+        <v>23.51055717468262</v>
       </c>
       <c r="C134" t="n">
         <v>24.11000061035156</v>
@@ -3695,11 +3707,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>22.85721969604492</v>
+        <v>22.85721778869629</v>
       </c>
       <c r="C135" t="n">
         <v>23.44000053405762</v>
@@ -3722,7 +3734,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
@@ -3751,11 +3763,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>26.9820442199707</v>
+        <v>26.98204612731934</v>
       </c>
       <c r="C137" t="n">
         <v>27.67000007629395</v>
@@ -3780,11 +3792,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>30.00497436523438</v>
+        <v>30.00497245788574</v>
       </c>
       <c r="C138" t="n">
         <v>30.77000045776367</v>
@@ -3809,11 +3821,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>29.11759567260742</v>
+        <v>29.11759757995605</v>
       </c>
       <c r="C139" t="n">
         <v>29.86000061035156</v>
@@ -3838,11 +3850,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>27.42086029052734</v>
+        <v>27.42085647583008</v>
       </c>
       <c r="C140" t="n">
         <v>28.1200008392334</v>
@@ -3867,11 +3879,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>31.17513275146484</v>
+        <v>31.17513465881348</v>
       </c>
       <c r="C141" t="n">
         <v>31.96999931335449</v>
@@ -3896,7 +3908,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
@@ -3925,11 +3937,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>43.20832824707031</v>
+        <v>43.20832443237305</v>
       </c>
       <c r="C143" t="n">
         <v>44.31000137329102</v>
@@ -3954,11 +3966,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>41.33606338500977</v>
+        <v>41.3360710144043</v>
       </c>
       <c r="C144" t="n">
         <v>42.38999938964844</v>
@@ -3983,11 +3995,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>40.09763717651367</v>
+        <v>40.0976448059082</v>
       </c>
       <c r="C145" t="n">
         <v>41.11999893188477</v>
@@ -4012,11 +4024,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>42.63299560546875</v>
+        <v>42.63299942016602</v>
       </c>
       <c r="C146" t="n">
         <v>43.72000122070312</v>
@@ -4041,11 +4053,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>47.596435546875</v>
+        <v>47.59645462036133</v>
       </c>
       <c r="C147" t="n">
         <v>48.81000137329102</v>
@@ -4070,11 +4082,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>50.84365081787109</v>
+        <v>50.84365463256836</v>
       </c>
       <c r="C148" t="n">
         <v>52.13999938964844</v>
@@ -4099,11 +4111,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>44.83679962158203</v>
+        <v>44.8368034362793</v>
       </c>
       <c r="C149" t="n">
         <v>45.97999954223633</v>
@@ -4128,11 +4140,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>56.15813446044922</v>
+        <v>56.15815353393555</v>
       </c>
       <c r="C150" t="n">
         <v>57.59000015258789</v>
@@ -4157,11 +4169,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>51.13619232177734</v>
+        <v>51.13618850708008</v>
       </c>
       <c r="C151" t="n">
         <v>52.43999862670898</v>
@@ -4186,7 +4198,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
@@ -4215,11 +4227,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>51.21420288085938</v>
+        <v>51.21421051025391</v>
       </c>
       <c r="C153" t="n">
         <v>52.52000045776367</v>
@@ -4244,11 +4256,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>44.1054573059082</v>
+        <v>44.10546112060547</v>
       </c>
       <c r="C154" t="n">
         <v>45.22999954223633</v>
@@ -4273,11 +4285,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>36.78217697143555</v>
+        <v>36.78216934204102</v>
       </c>
       <c r="C155" t="n">
         <v>37.72000122070312</v>
@@ -4302,11 +4314,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>37.60129165649414</v>
+        <v>37.60128784179688</v>
       </c>
       <c r="C156" t="n">
         <v>38.56000137329102</v>
@@ -4331,7 +4343,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
@@ -4360,11 +4372,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>37.26974105834961</v>
+        <v>37.26973724365234</v>
       </c>
       <c r="C158" t="n">
         <v>38.22000122070312</v>
@@ -4389,11 +4401,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>39.86360549926758</v>
+        <v>39.86360168457031</v>
       </c>
       <c r="C159" t="n">
         <v>40.88000106811523</v>
@@ -4418,11 +4430,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>40.30241775512695</v>
+        <v>40.30242919921875</v>
       </c>
       <c r="C160" t="n">
         <v>41.33000183105469</v>
@@ -4447,11 +4459,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>41.0142707824707</v>
+        <v>41.01427841186523</v>
       </c>
       <c r="C161" t="n">
         <v>42.06000137329102</v>
@@ -4476,11 +4488,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>31.79922866821289</v>
+        <v>31.79922676086426</v>
       </c>
       <c r="C162" t="n">
         <v>32.61000061035156</v>
@@ -4505,11 +4517,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>37.63053894042969</v>
+        <v>37.63055038452148</v>
       </c>
       <c r="C163" t="n">
         <v>38.59000015258789</v>
@@ -4534,7 +4546,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
@@ -4563,11 +4575,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>44.14446258544922</v>
+        <v>44.14446640014648</v>
       </c>
       <c r="C165" t="n">
         <v>45.27000045776367</v>
@@ -4592,11 +4604,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>41.78463363647461</v>
+        <v>41.78462219238281</v>
       </c>
       <c r="C166" t="n">
         <v>42.84999847412109</v>
@@ -4621,11 +4633,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>46.36777877807617</v>
+        <v>46.36777496337891</v>
       </c>
       <c r="C167" t="n">
         <v>47.54999923706055</v>
@@ -4650,7 +4662,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
@@ -4679,11 +4691,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>52.44287490844727</v>
+        <v>52.44287109375</v>
       </c>
       <c r="C169" t="n">
         <v>53.77999877929688</v>
@@ -4708,11 +4720,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>51.77002716064453</v>
+        <v>51.77003479003906</v>
       </c>
       <c r="C170" t="n">
         <v>53.09000015258789</v>
@@ -4737,7 +4749,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
@@ -4766,11 +4778,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>41.0142707824707</v>
+        <v>41.01427841186523</v>
       </c>
       <c r="C172" t="n">
         <v>42.06000137329102</v>
@@ -4795,11 +4807,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>46.69931793212891</v>
+        <v>46.69932174682617</v>
       </c>
       <c r="C173" t="n">
         <v>47.88999938964844</v>
@@ -4824,11 +4836,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>46.71882629394531</v>
+        <v>46.71881866455078</v>
       </c>
       <c r="C174" t="n">
         <v>47.90999984741211</v>
@@ -4853,11 +4865,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>50.23905944824219</v>
+        <v>50.23907089233398</v>
       </c>
       <c r="C175" t="n">
         <v>51.52000045776367</v>
@@ -4882,7 +4894,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
@@ -4911,7 +4923,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
@@ -4940,11 +4952,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>45.79244232177734</v>
+        <v>45.79244613647461</v>
       </c>
       <c r="C178" t="n">
         <v>46.95999908447266</v>
@@ -4969,11 +4981,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>49.08840560913086</v>
+        <v>49.08840942382812</v>
       </c>
       <c r="C179" t="n">
         <v>50.34000015258789</v>
@@ -4998,7 +5010,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
@@ -5027,11 +5039,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>73.31082153320312</v>
+        <v>73.31081390380859</v>
       </c>
       <c r="C181" t="n">
         <v>75.18000030517578</v>
@@ -5056,11 +5068,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>76.32398223876953</v>
+        <v>76.32398986816406</v>
       </c>
       <c r="C182" t="n">
         <v>78.26999664306641</v>
@@ -5085,7 +5097,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
@@ -5114,11 +5126,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>86.01686096191406</v>
+        <v>86.01686859130859</v>
       </c>
       <c r="C184" t="n">
         <v>88.20999908447266</v>
@@ -5143,11 +5155,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>83.93006134033203</v>
+        <v>83.93006896972656</v>
       </c>
       <c r="C185" t="n">
         <v>86.06999969482422</v>
@@ -5172,11 +5184,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>82.04804229736328</v>
+        <v>82.04803466796875</v>
       </c>
       <c r="C186" t="n">
         <v>84.13999938964844</v>
@@ -5201,11 +5213,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>82.86714935302734</v>
+        <v>82.86717224121094</v>
       </c>
       <c r="C187" t="n">
         <v>84.98000335693359</v>
@@ -5230,11 +5242,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>75.65114593505859</v>
+        <v>75.65113830566406</v>
       </c>
       <c r="C188" t="n">
         <v>77.58000183105469</v>
@@ -5259,7 +5271,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
@@ -5288,7 +5300,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
@@ -5317,11 +5329,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>67.47615814208984</v>
+        <v>67.47616577148438</v>
       </c>
       <c r="C191" t="n">
         <v>69.09999847412109</v>
@@ -5346,11 +5358,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>82.02602386474609</v>
+        <v>82.02600860595703</v>
       </c>
       <c r="C192" t="n">
         <v>84</v>
@@ -5375,7 +5387,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
@@ -5404,11 +5416,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>80.42234039306641</v>
+        <v>80.42233276367188</v>
       </c>
       <c r="C194" t="n">
         <v>82.26999664306641</v>
@@ -5433,7 +5445,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
@@ -5462,7 +5474,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
@@ -5491,11 +5503,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>66.74964141845703</v>
+        <v>66.7496337890625</v>
       </c>
       <c r="C197" t="n">
         <v>68.19000244140625</v>
@@ -5520,11 +5532,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>72.28029632568359</v>
+        <v>72.28028869628906</v>
       </c>
       <c r="C198" t="n">
         <v>73.83999633789062</v>
@@ -5549,11 +5561,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>54.11232757568359</v>
+        <v>54.11233139038086</v>
       </c>
       <c r="C199" t="n">
         <v>55.27999877929688</v>
@@ -5578,7 +5590,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
@@ -5607,7 +5619,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
@@ -5636,11 +5648,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>49.13776016235352</v>
+        <v>49.13776779174805</v>
       </c>
       <c r="C202" t="n">
         <v>50.09999847412109</v>
@@ -5665,7 +5677,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
@@ -5694,11 +5706,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>56.66207122802734</v>
+        <v>56.66206741333008</v>
       </c>
       <c r="C204" t="n">
         <v>57.65000152587891</v>
@@ -5723,11 +5735,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>49.23529052734375</v>
+        <v>49.23528671264648</v>
       </c>
       <c r="C205" t="n">
         <v>49.97999954223633</v>
@@ -5752,11 +5764,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>59.40151596069336</v>
+        <v>59.40151977539062</v>
       </c>
       <c r="C206" t="n">
         <v>60.29999923706055</v>
@@ -5781,11 +5793,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>56.95846939086914</v>
+        <v>56.95847702026367</v>
       </c>
       <c r="C207" t="n">
         <v>57.81999969482422</v>
@@ -5810,7 +5822,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
@@ -5839,11 +5851,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>63.52915191650391</v>
+        <v>63.52914810180664</v>
       </c>
       <c r="C209" t="n">
         <v>64.36000061035156</v>
@@ -5868,11 +5880,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>67.319580078125</v>
+        <v>67.31957244873047</v>
       </c>
       <c r="C210" t="n">
         <v>68.19999694824219</v>
@@ -5897,11 +5909,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>62.2952880859375</v>
+        <v>62.29528427124023</v>
       </c>
       <c r="C211" t="n">
         <v>63.11000061035156</v>
@@ -5924,11 +5936,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>70.60097503662109</v>
+        <v>70.60099792480469</v>
       </c>
       <c r="C212" t="n">
         <v>71.38999938964844</v>
@@ -5951,11 +5963,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>69.16703796386719</v>
+        <v>69.16703033447266</v>
       </c>
       <c r="C213" t="n">
         <v>69.94000244140625</v>
@@ -5978,7 +5990,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
@@ -6005,11 +6017,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>66.24127197265625</v>
+        <v>66.24127960205078</v>
       </c>
       <c r="C215" t="n">
         <v>66.87000274658203</v>
@@ -6032,11 +6044,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>75.40432739257812</v>
+        <v>75.40430450439453</v>
       </c>
       <c r="C216" t="n">
         <v>76.12000274658203</v>
@@ -6059,11 +6071,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>84.65081787109375</v>
+        <v>84.65081024169922</v>
       </c>
       <c r="C217" t="n">
         <v>85.33999633789062</v>
@@ -6086,11 +6098,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>85.05751037597656</v>
+        <v>85.05750274658203</v>
       </c>
       <c r="C218" t="n">
         <v>85.75</v>
@@ -6113,7 +6125,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
@@ -6140,11 +6152,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>117.0508270263672</v>
+        <v>117.0508346557617</v>
       </c>
       <c r="C220" t="n">
         <v>117.8899993896484</v>
@@ -6167,11 +6179,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>112.1559371948242</v>
+        <v>112.1559219360352</v>
       </c>
       <c r="C221" t="n">
         <v>112.9599990844727</v>
@@ -6194,11 +6206,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>124.1102142333984</v>
+        <v>124.1102294921875</v>
       </c>
       <c r="C222" t="n">
         <v>125</v>
@@ -6221,7 +6233,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
@@ -6248,11 +6260,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>109.1336441040039</v>
+        <v>109.1336364746094</v>
       </c>
       <c r="C224" t="n">
         <v>109.8199996948242</v>
@@ -6275,11 +6287,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>95.63851928710938</v>
+        <v>95.63851165771484</v>
       </c>
       <c r="C225" t="n">
         <v>96.23999786376953</v>
@@ -6302,11 +6314,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>103.0618362426758</v>
+        <v>103.0618286132812</v>
       </c>
       <c r="C226" t="n">
         <v>103.7099990844727</v>
@@ -6329,11 +6341,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>99.13870239257812</v>
+        <v>99.13871765136719</v>
       </c>
       <c r="C227" t="n">
         <v>99.65000152587891</v>
@@ -6358,7 +6370,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -6387,7 +6399,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -6416,7 +6428,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6445,7 +6457,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6474,11 +6486,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>86.669189453125</v>
+        <v>86.66917419433594</v>
       </c>
       <c r="C232" t="n">
         <v>86.88999938964844</v>
@@ -6503,11 +6515,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>76.75444030761719</v>
+        <v>76.75445556640625</v>
       </c>
       <c r="C233" t="n">
         <v>76.94999694824219</v>
@@ -6532,7 +6544,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6561,11 +6573,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>122.9367828369141</v>
+        <v>122.9367752075195</v>
       </c>
       <c r="C235" t="n">
         <v>123.25</v>
@@ -6590,7 +6602,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6619,11 +6631,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>118.8192901611328</v>
+        <v>118.8192977905273</v>
       </c>
       <c r="C237" t="n">
         <v>119.0100021362305</v>
@@ -6648,7 +6660,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6677,7 +6689,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6706,11 +6718,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>236.2489013671875</v>
+        <v>236.2489166259766</v>
       </c>
       <c r="C240" t="n">
         <v>236.4799957275391</v>
@@ -6735,7 +6747,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6764,7 +6776,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6793,7 +6805,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6822,7 +6834,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -6851,7 +6863,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -6880,7 +6892,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -6909,7 +6921,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -6938,7 +6950,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -6967,7 +6979,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -6996,32 +7008,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>1071.880004882812</v>
+        <v>1080.530029296875</v>
       </c>
       <c r="C250" t="n">
-        <v>1071.880004882812</v>
+        <v>1080.530029296875</v>
       </c>
       <c r="D250" t="n">
-        <v>411534500</v>
+        <v>433638900</v>
       </c>
       <c r="E250" t="n">
         <v>44.17</v>
       </c>
       <c r="F250" t="n">
-        <v>24.26714975962899</v>
+        <v>24.46298458901687</v>
       </c>
       <c r="G250" t="n">
         <v>1129393151</v>
       </c>
       <c r="H250" t="n">
-        <v>1210573936208.495</v>
+        <v>1220343214537.72</v>
       </c>
       <c r="I250" t="n">
-        <v>0.3643855106041811</v>
+        <v>0.3839574373335295</v>
       </c>
     </row>
   </sheetData>
@@ -7053,75 +7065,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39689</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39786</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40190</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7157,13 +7169,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40060</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40150</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40190</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7199,13 +7211,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40151</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40241</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40645</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7241,13 +7253,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40242</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40332</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40736</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7283,13 +7295,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40333</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40423</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40841</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7316,7 +7328,7 @@
       <c r="I6" t="n">
         <v>1.86</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>40841</v>
       </c>
       <c r="K6" t="n">
@@ -7329,13 +7341,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40424</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40514</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40554</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7362,7 +7374,7 @@
       <c r="I7" t="n">
         <v>1.78</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40841</v>
       </c>
       <c r="K7" t="n">
@@ -7375,13 +7387,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40515</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40605</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40645</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7408,7 +7420,7 @@
       <c r="I8" t="n">
         <v>1.46</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40841</v>
       </c>
       <c r="K8" t="n">
@@ -7421,13 +7433,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40606</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40696</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40736</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7454,7 +7466,7 @@
       <c r="I9" t="n">
         <v>0.61</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40841</v>
       </c>
       <c r="K9" t="n">
@@ -7467,13 +7479,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40697</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40787</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40841</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7500,7 +7512,7 @@
       <c r="I10" t="n">
         <v>0.15</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40841</v>
       </c>
       <c r="K10" t="n">
@@ -7513,13 +7525,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40788</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40878</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40918</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7546,7 +7558,7 @@
       <c r="I11" t="n">
         <v>-0.19</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40918</v>
       </c>
       <c r="K11" t="n">
@@ -7559,13 +7571,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40879</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40969</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>41008</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7592,7 +7604,7 @@
       <c r="I12" t="n">
         <v>-0.55</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>41008</v>
       </c>
       <c r="K12" t="n">
@@ -7605,13 +7617,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40970</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41060</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>41099</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7638,7 +7650,7 @@
       <c r="I13" t="n">
         <v>-0.9400000000000001</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>41099</v>
       </c>
       <c r="K13" t="n">
@@ -7651,13 +7663,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41061</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41151</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>41211</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7684,7 +7696,7 @@
       <c r="I14" t="n">
         <v>-1.04</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>41211</v>
       </c>
       <c r="K14" t="n">
@@ -7697,13 +7709,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41152</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41242</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41281</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7730,7 +7742,7 @@
       <c r="I15" t="n">
         <v>-1.12</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41281</v>
       </c>
       <c r="K15" t="n">
@@ -7743,13 +7755,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41243</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41333</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41372</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7776,7 +7788,7 @@
       <c r="I16" t="n">
         <v>-1.11</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41372</v>
       </c>
       <c r="K16" t="n">
@@ -7789,13 +7801,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41334</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41424</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41463</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7822,7 +7834,7 @@
       <c r="I17" t="n">
         <v>-0.75</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41463</v>
       </c>
       <c r="K17" t="n">
@@ -7835,13 +7847,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41425</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41515</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41575</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7868,7 +7880,7 @@
       <c r="I18" t="n">
         <v>1</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41575</v>
       </c>
       <c r="K18" t="n">
@@ -7881,13 +7893,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41516</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41606</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41646</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -7914,7 +7926,7 @@
       <c r="I19" t="n">
         <v>1.57</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41646</v>
       </c>
       <c r="K19" t="n">
@@ -7927,13 +7939,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41607</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41697</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41736</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -7960,7 +7972,7 @@
       <c r="I20" t="n">
         <v>2.46</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41736</v>
       </c>
       <c r="K20" t="n">
@@ -7973,13 +7985,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41698</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41788</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41823</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8006,7 +8018,7 @@
       <c r="I21" t="n">
         <v>3.1</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41823</v>
       </c>
       <c r="K21" t="n">
@@ -8019,13 +8031,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41789</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41879</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41939</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8052,7 +8064,7 @@
       <c r="I22" t="n">
         <v>2.55</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41939</v>
       </c>
       <c r="K22" t="n">
@@ -8065,13 +8077,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41880</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41977</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>42013</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8098,7 +8110,7 @@
       <c r="I23" t="n">
         <v>3.09</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>42013</v>
       </c>
       <c r="K23" t="n">
@@ -8111,13 +8123,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41978</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42068</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>42104</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8144,7 +8156,7 @@
       <c r="I24" t="n">
         <v>3.26</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>42104</v>
       </c>
       <c r="K24" t="n">
@@ -8157,13 +8169,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42069</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42159</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>42195</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8190,7 +8202,7 @@
       <c r="I25" t="n">
         <v>3</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>42195</v>
       </c>
       <c r="K25" t="n">
@@ -8203,13 +8215,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42160</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42250</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42304</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8236,7 +8248,7 @@
       <c r="I26" t="n">
         <v>2.46</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42304</v>
       </c>
       <c r="K26" t="n">
@@ -8249,13 +8261,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42251</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42341</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42377</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8282,7 +8294,7 @@
       <c r="I27" t="n">
         <v>1.81</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42377</v>
       </c>
       <c r="K27" t="n">
@@ -8295,13 +8307,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42342</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42432</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42468</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8328,7 +8340,7 @@
       <c r="I28" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42468</v>
       </c>
       <c r="K28" t="n">
@@ -8341,13 +8353,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42433</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42523</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42557</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8374,7 +8386,7 @@
       <c r="I29" t="n">
         <v>0.3100000000000001</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42557</v>
       </c>
       <c r="K29" t="n">
@@ -8387,13 +8399,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42524</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42614</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42671</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8420,7 +8432,7 @@
       <c r="I30" t="n">
         <v>-0.27</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42671</v>
       </c>
       <c r="K30" t="n">
@@ -8433,13 +8445,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42615</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42705</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42744</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8466,7 +8478,7 @@
       <c r="I31" t="n">
         <v>-0.3</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42744</v>
       </c>
       <c r="K31" t="n">
@@ -8479,13 +8491,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42706</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42796</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42822</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8512,7 +8524,7 @@
       <c r="I32" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42822</v>
       </c>
       <c r="K32" t="n">
@@ -8525,13 +8537,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42797</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42887</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8558,7 +8570,7 @@
       <c r="I33" t="n">
         <v>2.17</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="K33" t="n">
@@ -8571,13 +8583,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42888</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42978</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8604,7 +8616,7 @@
       <c r="I34" t="n">
         <v>4.32</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="K34" t="n">
@@ -8617,13 +8629,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42979</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43069</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>43089</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8650,7 +8662,7 @@
       <c r="I35" t="n">
         <v>6.35</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>43089</v>
       </c>
       <c r="K35" t="n">
@@ -8663,13 +8675,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43070</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43160</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>43182</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8696,7 +8708,7 @@
       <c r="I36" t="n">
         <v>8.25</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>43182</v>
       </c>
       <c r="K36" t="n">
@@ -8709,13 +8721,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43161</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43251</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43273</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8742,7 +8754,7 @@
       <c r="I37" t="n">
         <v>9.949999999999999</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43273</v>
       </c>
       <c r="K37" t="n">
@@ -8755,13 +8767,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43252</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43342</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43388</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8788,7 +8800,7 @@
       <c r="I38" t="n">
         <v>11.52</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43388</v>
       </c>
       <c r="K38" t="n">
@@ -8801,13 +8813,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43343</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43433</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43453</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8834,7 +8846,7 @@
       <c r="I39" t="n">
         <v>12.14</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43453</v>
       </c>
       <c r="K39" t="n">
@@ -8847,13 +8859,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43434</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43524</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43545</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -8880,7 +8892,7 @@
       <c r="I40" t="n">
         <v>10.89</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43545</v>
       </c>
       <c r="K40" t="n">
@@ -8893,13 +8905,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43525</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43615</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43642</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -8926,7 +8938,7 @@
       <c r="I41" t="n">
         <v>8.530000000000001</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43642</v>
       </c>
       <c r="K41" t="n">
@@ -8939,13 +8951,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43616</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43706</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43755</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -8972,7 +8984,7 @@
       <c r="I42" t="n">
         <v>5.46</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43755</v>
       </c>
       <c r="K42" t="n">
@@ -8985,13 +8997,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43707</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43797</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43819</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9018,7 +9030,7 @@
       <c r="I43" t="n">
         <v>3.08</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43819</v>
       </c>
       <c r="K43" t="n">
@@ -9031,13 +9043,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43798</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43888</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43916</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9064,7 +9076,7 @@
       <c r="I44" t="n">
         <v>2.02</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43916</v>
       </c>
       <c r="K44" t="n">
@@ -9077,13 +9089,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43889</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43979</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>44011</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9110,7 +9122,7 @@
       <c r="I45" t="n">
         <v>1.99</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>44011</v>
       </c>
       <c r="K45" t="n">
@@ -9123,13 +9135,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43980</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44077</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>44123</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9156,7 +9168,7 @@
       <c r="I46" t="n">
         <v>2.37</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>44123</v>
       </c>
       <c r="K46" t="n">
@@ -9169,13 +9181,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44078</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44168</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>44204</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9202,7 +9214,7 @@
       <c r="I47" t="n">
         <v>2.65</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>44204</v>
       </c>
       <c r="K47" t="n">
@@ -9215,13 +9227,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44169</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44259</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44287</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9248,7 +9260,7 @@
       <c r="I48" t="n">
         <v>2.82</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44287</v>
       </c>
       <c r="K48" t="n">
@@ -9261,13 +9273,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44260</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44350</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44378</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9294,7 +9306,7 @@
       <c r="I49" t="n">
         <v>3.63</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44378</v>
       </c>
       <c r="K49" t="n">
@@ -9307,13 +9319,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44351</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44441</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44477</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9340,7 +9352,7 @@
       <c r="I50" t="n">
         <v>5.140000000000001</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44477</v>
       </c>
       <c r="K50" t="n">
@@ -9353,13 +9365,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44442</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44532</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44567</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9386,7 +9398,7 @@
       <c r="I51" t="n">
         <v>6.470000000000001</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44567</v>
       </c>
       <c r="K51" t="n">
@@ -9399,13 +9411,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44533</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44623</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44650</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9432,7 +9444,7 @@
       <c r="I52" t="n">
         <v>7.94</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44650</v>
       </c>
       <c r="K52" t="n">
@@ -9445,13 +9457,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44624</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44714</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9478,7 +9490,7 @@
       <c r="I53" t="n">
         <v>8.76</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="K53" t="n">
@@ -9491,13 +9503,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44715</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44805</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44841</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9524,7 +9536,7 @@
       <c r="I54" t="n">
         <v>7.75</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44841</v>
       </c>
       <c r="K54" t="n">
@@ -9537,13 +9549,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44806</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44896</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44917</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9570,7 +9582,7 @@
       <c r="I55" t="n">
         <v>5.53</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44917</v>
       </c>
       <c r="K55" t="n">
@@ -9583,13 +9595,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44897</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44987</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>45014</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9616,7 +9628,7 @@
       <c r="I56" t="n">
         <v>1.41</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>45014</v>
       </c>
       <c r="K56" t="n">
@@ -9629,13 +9641,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44988</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45078</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>45106</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9662,7 +9674,7 @@
       <c r="I57" t="n">
         <v>-2.66</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>45106</v>
       </c>
       <c r="K57" t="n">
@@ -9675,13 +9687,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45079</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45169</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>45205</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9708,7 +9720,7 @@
       <c r="I58" t="n">
         <v>-5.34</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>45205</v>
       </c>
       <c r="K58" t="n">
@@ -9721,13 +9733,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45170</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45260</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45281</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9754,7 +9766,7 @@
       <c r="I59" t="n">
         <v>-6.28</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45281</v>
       </c>
       <c r="K59" t="n">
@@ -9767,13 +9779,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45261</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45351</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45372</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9800,7 +9812,7 @@
       <c r="I60" t="n">
         <v>-3.45</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45372</v>
       </c>
       <c r="K60" t="n">
@@ -9813,13 +9825,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45352</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45442</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45470</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9846,7 +9858,7 @@
       <c r="I61" t="n">
         <v>-1.42</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45470</v>
       </c>
       <c r="K61" t="n">
@@ -9859,13 +9871,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45443</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45533</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45569</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -9892,7 +9904,7 @@
       <c r="I62" t="n">
         <v>0.7</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45569</v>
       </c>
       <c r="K62" t="n">
@@ -9905,13 +9917,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45534</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45624</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45645</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -9938,7 +9950,7 @@
       <c r="I63" t="n">
         <v>3.49</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45645</v>
       </c>
       <c r="K63" t="n">
@@ -9951,13 +9963,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45625</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45715</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45737</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -9984,7 +9996,7 @@
       <c r="I64" t="n">
         <v>4.19</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45737</v>
       </c>
       <c r="K64" t="n">
@@ -9997,13 +10009,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45716</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45806</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45834</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10030,7 +10042,7 @@
       <c r="I65" t="n">
         <v>5.57</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45834</v>
       </c>
       <c r="K65" t="n">
@@ -10043,13 +10055,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45807</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45897</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45933</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10076,7 +10088,7 @@
       <c r="I66" t="n">
         <v>7.59</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45933</v>
       </c>
       <c r="K66" t="n">
@@ -10089,13 +10101,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45898</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45988</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>46009</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10122,7 +10134,7 @@
       <c r="I67" t="n">
         <v>10.52</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>46009</v>
       </c>
       <c r="K67" t="n">
@@ -10135,13 +10147,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45989</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46079</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>46100</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10168,7 +10180,7 @@
       <c r="I68" t="n">
         <v>21.18</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>46100</v>
       </c>
       <c r="K68" t="n">
@@ -10181,13 +10193,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46080</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46170</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>46198</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10214,7 +10226,7 @@
       <c r="I69" t="n">
         <v>44.17</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>46198</v>
       </c>
       <c r="K69" t="n">
@@ -10251,52 +10263,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40150</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40190</v>
       </c>
       <c r="C2" t="n">
@@ -10325,10 +10337,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40547</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40554</v>
       </c>
       <c r="C3" t="n">
@@ -10357,10 +10369,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40638</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40645</v>
       </c>
       <c r="C4" t="n">
@@ -10389,10 +10401,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40729</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40736</v>
       </c>
       <c r="C5" t="n">
@@ -10421,10 +10433,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40834</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40841</v>
       </c>
       <c r="C6" t="n">
@@ -10453,10 +10465,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40911</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40918</v>
       </c>
       <c r="C7" t="n">
@@ -10485,10 +10497,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>41001</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>41008</v>
       </c>
       <c r="C8" t="n">
@@ -10517,10 +10529,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>41093</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>41099</v>
       </c>
       <c r="C9" t="n">
@@ -10549,10 +10561,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>41200</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>41211</v>
       </c>
       <c r="C10" t="n">
@@ -10581,10 +10593,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>41281</v>
       </c>
       <c r="C11" t="n">
@@ -10613,10 +10625,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41366</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41372</v>
       </c>
       <c r="C12" t="n">
@@ -10645,10 +10657,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41463</v>
       </c>
       <c r="C13" t="n">
@@ -10677,10 +10689,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41565</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41575</v>
       </c>
       <c r="C14" t="n">
@@ -10709,10 +10721,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41641</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41646</v>
       </c>
       <c r="C15" t="n">
@@ -10741,10 +10753,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41732</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41736</v>
       </c>
       <c r="C16" t="n">
@@ -10773,10 +10785,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41816</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41823</v>
       </c>
       <c r="C17" t="n">
@@ -10805,10 +10817,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41928</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41939</v>
       </c>
       <c r="C18" t="n">
@@ -10837,10 +10849,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>42006</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>42013</v>
       </c>
       <c r="C19" t="n">
@@ -10869,10 +10881,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>42097</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>42104</v>
       </c>
       <c r="C20" t="n">
@@ -10901,10 +10913,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>42191</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>42195</v>
       </c>
       <c r="C21" t="n">
@@ -10933,10 +10945,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42298</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>42304</v>
       </c>
       <c r="C22" t="n">
@@ -10965,10 +10977,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42376</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42377</v>
       </c>
       <c r="C23" t="n">
@@ -10997,10 +11009,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42468</v>
       </c>
       <c r="C24" t="n">
@@ -11029,10 +11041,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42557</v>
       </c>
       <c r="C25" t="n">
@@ -11061,10 +11073,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42664</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42671</v>
       </c>
       <c r="C26" t="n">
@@ -11093,10 +11105,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42738</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42744</v>
       </c>
       <c r="C27" t="n">
@@ -11125,10 +11137,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42815</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42822</v>
       </c>
       <c r="C28" t="n">
@@ -11157,10 +11169,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42909</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="C29" t="n">
@@ -11189,10 +11201,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>43028</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="C30" t="n">
@@ -11221,10 +11233,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>43084</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>43089</v>
       </c>
       <c r="C31" t="n">
@@ -11253,10 +11265,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>43175</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>43182</v>
       </c>
       <c r="C32" t="n">
@@ -11285,10 +11297,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43266</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>43273</v>
       </c>
       <c r="C33" t="n">
@@ -11317,10 +11329,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43381</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43388</v>
       </c>
       <c r="C34" t="n">
@@ -11349,10 +11361,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43446</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43453</v>
       </c>
       <c r="C35" t="n">
@@ -11381,10 +11393,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43538</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43545</v>
       </c>
       <c r="C36" t="n">
@@ -11413,10 +11425,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43635</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43642</v>
       </c>
       <c r="C37" t="n">
@@ -11445,10 +11457,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43748</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43755</v>
       </c>
       <c r="C38" t="n">
@@ -11477,10 +11489,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43812</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43819</v>
       </c>
       <c r="C39" t="n">
@@ -11509,10 +11521,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43909</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43916</v>
       </c>
       <c r="C40" t="n">
@@ -11541,10 +11553,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>44005</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>44011</v>
       </c>
       <c r="C41" t="n">
@@ -11573,10 +11585,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>44113</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>44123</v>
       </c>
       <c r="C42" t="n">
@@ -11605,10 +11617,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>44200</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>44204</v>
       </c>
       <c r="C43" t="n">
@@ -11637,10 +11649,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44280</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>44287</v>
       </c>
       <c r="C44" t="n">
@@ -11669,10 +11681,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44371</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44378</v>
       </c>
       <c r="C45" t="n">
@@ -11701,10 +11713,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44477</v>
       </c>
       <c r="C46" t="n">
@@ -11733,10 +11745,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44564</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44567</v>
       </c>
       <c r="C47" t="n">
@@ -11765,10 +11777,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44644</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44650</v>
       </c>
       <c r="C48" t="n">
@@ -11797,10 +11809,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44736</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="C49" t="n">
@@ -11829,10 +11841,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44841</v>
       </c>
       <c r="C50" t="n">
@@ -11861,10 +11873,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44911</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44917</v>
       </c>
       <c r="C51" t="n">
@@ -11893,10 +11905,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>45008</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>45014</v>
       </c>
       <c r="C52" t="n">
@@ -11925,10 +11937,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>45099</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>45106</v>
       </c>
       <c r="C53" t="n">
@@ -11957,10 +11969,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45198</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>45205</v>
       </c>
       <c r="C54" t="n">
@@ -11989,10 +12001,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45274</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>45281</v>
       </c>
       <c r="C55" t="n">
@@ -12021,10 +12033,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45365</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45372</v>
       </c>
       <c r="C56" t="n">
@@ -12053,10 +12065,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45463</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45470</v>
       </c>
       <c r="C57" t="n">
@@ -12085,10 +12097,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45562</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45569</v>
       </c>
       <c r="C58" t="n">
@@ -12117,10 +12129,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45638</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45645</v>
       </c>
       <c r="C59" t="n">
@@ -12149,10 +12161,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45729</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45737</v>
       </c>
       <c r="C60" t="n">
@@ -12181,10 +12193,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45826</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45834</v>
       </c>
       <c r="C61" t="n">
@@ -12213,10 +12225,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45926</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45933</v>
       </c>
       <c r="C62" t="n">
@@ -12245,10 +12257,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>46001</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>46009</v>
       </c>
       <c r="C63" t="n">
@@ -12277,10 +12289,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>46092</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>46100</v>
       </c>
       <c r="C64" t="n">
@@ -12309,10 +12321,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>46190</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>46198</v>
       </c>
       <c r="C65" t="n">
@@ -12359,12 +12371,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/MU.xlsx
+++ b/salidas/empresas/MU.xlsx
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>15.1243782043457</v>
+        <v>15.12437725067139</v>
       </c>
       <c r="C3" t="n">
         <v>15.51000022888184</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>14.3540210723877</v>
+        <v>14.35401916503906</v>
       </c>
       <c r="C4" t="n">
         <v>14.72000026702881</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>16.5480785369873</v>
+        <v>16.54807472229004</v>
       </c>
       <c r="C5" t="n">
         <v>16.96999931335449</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>16.14826965332031</v>
+        <v>16.14827156066895</v>
       </c>
       <c r="C6" t="n">
         <v>16.55999946594238</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>14.6855640411377</v>
+        <v>14.68556690216064</v>
       </c>
       <c r="C7" t="n">
         <v>15.0600004196167</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>15.20238876342773</v>
+        <v>15.20238590240479</v>
       </c>
       <c r="C8" t="n">
         <v>15.59000015258789</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>16.85037422180176</v>
+        <v>16.85037231445312</v>
       </c>
       <c r="C9" t="n">
         <v>17.28000068664551</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>16.96738433837891</v>
+        <v>16.96739196777344</v>
       </c>
       <c r="C10" t="n">
         <v>17.39999961853027</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>14.09073066711426</v>
+        <v>14.09073257446289</v>
       </c>
       <c r="C11" t="n">
         <v>14.44999980926514</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>14.23700332641602</v>
+        <v>14.23700428009033</v>
       </c>
       <c r="C12" t="n">
         <v>14.60000038146973</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>13.61291408538818</v>
+        <v>13.61291599273682</v>
       </c>
       <c r="C13" t="n">
         <v>13.96000003814697</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>12.62802600860596</v>
+        <v>12.62802696228027</v>
       </c>
       <c r="C14" t="n">
         <v>12.94999980926514</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>11.56512641906738</v>
+        <v>11.56512832641602</v>
       </c>
       <c r="C15" t="n">
         <v>11.85999965667725</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>11.77965641021729</v>
+        <v>11.77965450286865</v>
       </c>
       <c r="C16" t="n">
         <v>12.07999992370605</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>11.18482398986816</v>
+        <v>11.18482303619385</v>
       </c>
       <c r="C17" t="n">
         <v>11.47000026702881</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>11.57487773895264</v>
+        <v>11.57487678527832</v>
       </c>
       <c r="C20" t="n">
         <v>11.86999988555908</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>8.113141059875488</v>
+        <v>8.113142967224121</v>
       </c>
       <c r="C24" t="n">
         <v>8.319999694824219</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>7.06974458694458</v>
+        <v>7.069745063781738</v>
       </c>
       <c r="C25" t="n">
         <v>7.25</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>6.816208362579346</v>
+        <v>6.816208839416504</v>
       </c>
       <c r="C26" t="n">
         <v>6.989999771118164</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>7.333031177520752</v>
+        <v>7.33303165435791</v>
       </c>
       <c r="C27" t="n">
         <v>7.519999980926514</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>5.821567535400391</v>
+        <v>5.821568965911865</v>
       </c>
       <c r="C28" t="n">
         <v>5.96999979019165</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>7.528058528900146</v>
+        <v>7.528059005737305</v>
       </c>
       <c r="C29" t="n">
         <v>7.71999979019165</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>7.869357109069824</v>
+        <v>7.86935567855835</v>
       </c>
       <c r="C30" t="n">
         <v>8.069999694824219</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>5.850822925567627</v>
+        <v>5.850823402404785</v>
       </c>
       <c r="C31" t="n">
         <v>6</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>3.949306011199951</v>
+        <v>3.949306488037109</v>
       </c>
       <c r="C34" t="n">
         <v>4.050000190734863</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>4.592896461486816</v>
+        <v>4.592895984649658</v>
       </c>
       <c r="C35" t="n">
         <v>4.710000038146973</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>2.671876192092896</v>
+        <v>2.671875715255737</v>
       </c>
       <c r="C36" t="n">
         <v>2.740000009536743</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>3.627510070800781</v>
+        <v>3.627510786056519</v>
       </c>
       <c r="C38" t="n">
         <v>3.720000028610229</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>3.139941930770874</v>
+        <v>3.139941453933716</v>
       </c>
       <c r="C39" t="n">
         <v>3.220000028610229</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>4.758670330047607</v>
+        <v>4.758668899536133</v>
       </c>
       <c r="C41" t="n">
         <v>4.880000114440918</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>6.23112678527832</v>
+        <v>6.231125831604004</v>
       </c>
       <c r="C44" t="n">
         <v>6.389999866485596</v>
@@ -1334,7 +1334,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>7.996125221252441</v>
+        <v>7.9961256980896</v>
       </c>
       <c r="C46" t="n">
         <v>8.199999809265137</v>
@@ -1353,7 +1353,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>6.621181964874268</v>
+        <v>6.621181011199951</v>
       </c>
       <c r="C47" t="n">
         <v>6.789999961853027</v>
@@ -1372,7 +1372,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>7.333031177520752</v>
+        <v>7.33303165435791</v>
       </c>
       <c r="C48" t="n">
         <v>7.519999980926514</v>
@@ -1410,7 +1410,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>8.503196716308594</v>
+        <v>8.503194808959961</v>
       </c>
       <c r="C50" t="n">
         <v>8.720000267028809</v>
@@ -1435,7 +1435,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>8.834742546081543</v>
+        <v>8.834743499755859</v>
       </c>
       <c r="C51" t="n">
         <v>9.060000419616699</v>
@@ -1460,7 +1460,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>10.11217403411865</v>
+        <v>10.11217212677002</v>
       </c>
       <c r="C52" t="n">
         <v>10.36999988555908</v>
@@ -1485,7 +1485,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>9.117530822753906</v>
+        <v>9.117533683776855</v>
       </c>
       <c r="C53" t="n">
         <v>9.350000381469727</v>
@@ -1510,7 +1510,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>8.863997459411621</v>
+        <v>8.863998413085938</v>
       </c>
       <c r="C54" t="n">
         <v>9.090000152587891</v>
@@ -1585,7 +1585,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>6.299386024475098</v>
+        <v>6.299385547637939</v>
       </c>
       <c r="C57" t="n">
         <v>6.460000038146973</v>
@@ -1604,7 +1604,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>7.030739307403564</v>
+        <v>7.030737400054932</v>
       </c>
       <c r="C58" t="n">
         <v>7.210000038146973</v>
@@ -1642,7 +1642,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>7.089247703552246</v>
+        <v>7.089245796203613</v>
       </c>
       <c r="C60" t="n">
         <v>7.269999980926514</v>
@@ -1661,7 +1661,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>7.820600032806396</v>
+        <v>7.820600509643555</v>
       </c>
       <c r="C61" t="n">
         <v>8.020000457763672</v>
@@ -1680,7 +1680,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>10.27794742584229</v>
+        <v>10.27794456481934</v>
       </c>
       <c r="C62" t="n">
         <v>10.53999996185303</v>
@@ -1705,7 +1705,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>10.8532772064209</v>
+        <v>10.85327625274658</v>
       </c>
       <c r="C63" t="n">
         <v>11.13000011444092</v>
@@ -1730,7 +1730,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>11.18482398986816</v>
+        <v>11.18482303619385</v>
       </c>
       <c r="C64" t="n">
         <v>11.47000026702881</v>
@@ -1755,7 +1755,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>11.03855323791504</v>
+        <v>11.03855037689209</v>
       </c>
       <c r="C65" t="n">
         <v>11.31999969482422</v>
@@ -1880,7 +1880,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>4.914690971374512</v>
+        <v>4.91469144821167</v>
       </c>
       <c r="C70" t="n">
         <v>5.039999961853027</v>
@@ -1905,7 +1905,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>5.451017379760742</v>
+        <v>5.451016902923584</v>
       </c>
       <c r="C71" t="n">
         <v>5.590000152587891</v>
@@ -1934,7 +1934,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>5.841071605682373</v>
+        <v>5.841072082519531</v>
       </c>
       <c r="C72" t="n">
         <v>5.989999771118164</v>
@@ -1963,7 +1963,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>6.133612632751465</v>
+        <v>6.133613109588623</v>
       </c>
       <c r="C73" t="n">
         <v>6.289999961853027</v>
@@ -1992,7 +1992,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>7.4110426902771</v>
+        <v>7.411042213439941</v>
       </c>
       <c r="C74" t="n">
         <v>7.599999904632568</v>
@@ -2019,7 +2019,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>8.337423324584961</v>
+        <v>8.337424278259277</v>
       </c>
       <c r="C75" t="n">
         <v>8.550000190734863</v>
@@ -2046,7 +2046,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>7.898612022399902</v>
+        <v>7.898612976074219</v>
       </c>
       <c r="C76" t="n">
         <v>8.100000381469727</v>
@@ -2073,7 +2073,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>6.426154136657715</v>
+        <v>6.426155090332031</v>
       </c>
       <c r="C77" t="n">
         <v>6.590000152587891</v>
@@ -2100,7 +2100,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>5.694800853729248</v>
+        <v>5.694801330566406</v>
       </c>
       <c r="C78" t="n">
         <v>5.840000152587891</v>
@@ -2127,7 +2127,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>6.153115272521973</v>
+        <v>6.153114795684814</v>
       </c>
       <c r="C79" t="n">
         <v>6.309999942779541</v>
@@ -2154,7 +2154,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>6.055602073669434</v>
+        <v>6.055601596832275</v>
       </c>
       <c r="C80" t="n">
         <v>6.210000038146973</v>
@@ -2181,7 +2181,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>6.055602073669434</v>
+        <v>6.055601596832275</v>
       </c>
       <c r="C81" t="n">
         <v>6.210000038146973</v>
@@ -2235,7 +2235,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>5.294994831085205</v>
+        <v>5.294993877410889</v>
       </c>
       <c r="C83" t="n">
         <v>5.429999828338623</v>
@@ -2262,7 +2262,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>5.821567535400391</v>
+        <v>5.821568965911865</v>
       </c>
       <c r="C84" t="n">
         <v>5.96999979019165</v>
@@ -2289,7 +2289,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>6.182369232177734</v>
+        <v>6.182370185852051</v>
       </c>
       <c r="C85" t="n">
         <v>6.340000152587891</v>
@@ -2316,7 +2316,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>7.372036933898926</v>
+        <v>7.372037887573242</v>
       </c>
       <c r="C86" t="n">
         <v>7.559999942779541</v>
@@ -2343,7 +2343,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>8.171650886535645</v>
+        <v>8.171648979187012</v>
       </c>
       <c r="C87" t="n">
         <v>8.380000114440918</v>
@@ -2370,7 +2370,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>9.731864929199219</v>
+        <v>9.731869697570801</v>
       </c>
       <c r="C88" t="n">
         <v>9.979999542236328</v>
@@ -2397,7 +2397,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>9.185792922973633</v>
+        <v>9.185791969299316</v>
       </c>
       <c r="C89" t="n">
         <v>9.420000076293945</v>
@@ -2424,7 +2424,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>11.3896017074585</v>
+        <v>11.38960266113281</v>
       </c>
       <c r="C90" t="n">
         <v>11.68000030517578</v>
@@ -2478,7 +2478,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>12.910813331604</v>
+        <v>12.91081523895264</v>
       </c>
       <c r="C92" t="n">
         <v>13.23999977111816</v>
@@ -2505,7 +2505,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>13.23261070251465</v>
+        <v>13.23260974884033</v>
       </c>
       <c r="C93" t="n">
         <v>13.56999969482422</v>
@@ -2532,7 +2532,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>17.03564262390137</v>
+        <v>17.03564643859863</v>
       </c>
       <c r="C94" t="n">
         <v>17.46999931335449</v>
@@ -2675,7 +2675,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>23.58857154846191</v>
+        <v>23.58856964111328</v>
       </c>
       <c r="C99" t="n">
         <v>24.19000053405762</v>
@@ -2704,7 +2704,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>23.07174301147461</v>
+        <v>23.07173919677734</v>
       </c>
       <c r="C100" t="n">
         <v>23.65999984741211</v>
@@ -2733,7 +2733,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>25.47058296203613</v>
+        <v>25.47058868408203</v>
       </c>
       <c r="C101" t="n">
         <v>26.1200008392334</v>
@@ -2762,7 +2762,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>27.87917137145996</v>
+        <v>27.8791675567627</v>
       </c>
       <c r="C102" t="n">
         <v>28.59000015258789</v>
@@ -2820,7 +2820,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>29.79043960571289</v>
+        <v>29.79043388366699</v>
       </c>
       <c r="C104" t="n">
         <v>30.54999923706055</v>
@@ -2849,7 +2849,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>31.78946685791016</v>
+        <v>31.78947067260742</v>
       </c>
       <c r="C105" t="n">
         <v>32.59999847412109</v>
@@ -2878,7 +2878,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>33.40820693969727</v>
+        <v>33.408203125</v>
       </c>
       <c r="C106" t="n">
         <v>34.2599983215332</v>
@@ -2907,7 +2907,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>32.26729202270508</v>
+        <v>32.26728439331055</v>
       </c>
       <c r="C107" t="n">
         <v>33.09000015258789</v>
@@ -2936,7 +2936,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>35.05618286132812</v>
+        <v>35.05618667602539</v>
       </c>
       <c r="C108" t="n">
         <v>35.95000076293945</v>
@@ -2965,7 +2965,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>34.13954544067383</v>
+        <v>34.13954925537109</v>
       </c>
       <c r="C109" t="n">
         <v>35.0099983215332</v>
@@ -2994,7 +2994,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>28.54226684570312</v>
+        <v>28.54226493835449</v>
       </c>
       <c r="C110" t="n">
         <v>29.27000045776367</v>
@@ -3052,7 +3052,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>26.45546722412109</v>
+        <v>26.45547294616699</v>
       </c>
       <c r="C112" t="n">
         <v>27.1299991607666</v>
@@ -3139,7 +3139,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>18.37158584594727</v>
+        <v>18.37158393859863</v>
       </c>
       <c r="C115" t="n">
         <v>18.84000015258789</v>
@@ -3168,7 +3168,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>18.0497875213623</v>
+        <v>18.0497932434082</v>
       </c>
       <c r="C116" t="n">
         <v>18.51000022888184</v>
@@ -3226,7 +3226,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>14.60755348205566</v>
+        <v>14.60755443572998</v>
       </c>
       <c r="C118" t="n">
         <v>14.97999954223633</v>
@@ -3255,7 +3255,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>16.14826965332031</v>
+        <v>16.14827156066895</v>
       </c>
       <c r="C119" t="n">
         <v>16.55999946594238</v>
@@ -3284,7 +3284,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>15.53393459320068</v>
+        <v>15.53393650054932</v>
       </c>
       <c r="C120" t="n">
         <v>15.93000030517578</v>
@@ -3313,7 +3313,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>13.80794334411621</v>
+        <v>13.80794239044189</v>
       </c>
       <c r="C121" t="n">
         <v>14.15999984741211</v>
@@ -3371,7 +3371,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>10.36570739746094</v>
+        <v>10.36570835113525</v>
       </c>
       <c r="C123" t="n">
         <v>10.63000011444092</v>
@@ -3400,7 +3400,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>10.20968818664551</v>
+        <v>10.20968627929688</v>
       </c>
       <c r="C124" t="n">
         <v>10.47000026702881</v>
@@ -3429,7 +3429,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>10.4827241897583</v>
+        <v>10.48272609710693</v>
       </c>
       <c r="C125" t="n">
         <v>10.75</v>
@@ -3458,7 +3458,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>12.4037446975708</v>
+        <v>12.40374374389648</v>
       </c>
       <c r="C126" t="n">
         <v>12.72000026702881</v>
@@ -3487,7 +3487,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>13.41788959503174</v>
+        <v>13.41788673400879</v>
       </c>
       <c r="C127" t="n">
         <v>13.76000022888184</v>
@@ -3630,7 +3630,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>19.04442977905273</v>
+        <v>19.0444278717041</v>
       </c>
       <c r="C132" t="n">
         <v>19.53000068664551</v>
@@ -3657,7 +3657,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>21.37500953674316</v>
+        <v>21.3750057220459</v>
       </c>
       <c r="C133" t="n">
         <v>21.92000007629395</v>
@@ -3684,7 +3684,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>23.51055717468262</v>
+        <v>23.51055908203125</v>
       </c>
       <c r="C134" t="n">
         <v>24.11000061035156</v>
@@ -3738,7 +3738,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>28.18146133422852</v>
+        <v>28.18146514892578</v>
       </c>
       <c r="C136" t="n">
         <v>28.89999961853027</v>
@@ -3767,7 +3767,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>26.98204612731934</v>
+        <v>26.98204803466797</v>
       </c>
       <c r="C137" t="n">
         <v>27.67000007629395</v>
@@ -3825,7 +3825,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>29.11759757995605</v>
+        <v>29.11758995056152</v>
       </c>
       <c r="C139" t="n">
         <v>29.86000061035156</v>
@@ -3854,7 +3854,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>27.42085647583008</v>
+        <v>27.42086029052734</v>
       </c>
       <c r="C140" t="n">
         <v>28.1200008392334</v>
@@ -3883,7 +3883,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>31.17513465881348</v>
+        <v>31.17513656616211</v>
       </c>
       <c r="C141" t="n">
         <v>31.96999931335449</v>
@@ -3912,7 +3912,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>38.35214614868164</v>
+        <v>38.35215377807617</v>
       </c>
       <c r="C142" t="n">
         <v>39.33000183105469</v>
@@ -3941,7 +3941,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>43.20832443237305</v>
+        <v>43.20833206176758</v>
       </c>
       <c r="C143" t="n">
         <v>44.31000137329102</v>
@@ -3970,7 +3970,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>41.3360710144043</v>
+        <v>41.33605575561523</v>
       </c>
       <c r="C144" t="n">
         <v>42.38999938964844</v>
@@ -4028,7 +4028,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>42.63299942016602</v>
+        <v>42.63299560546875</v>
       </c>
       <c r="C146" t="n">
         <v>43.72000122070312</v>
@@ -4057,7 +4057,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>47.59645462036133</v>
+        <v>47.59644317626953</v>
       </c>
       <c r="C147" t="n">
         <v>48.81000137329102</v>
@@ -4086,7 +4086,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>50.84365463256836</v>
+        <v>50.84364318847656</v>
       </c>
       <c r="C148" t="n">
         <v>52.13999938964844</v>
@@ -4115,7 +4115,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>44.8368034362793</v>
+        <v>44.83679962158203</v>
       </c>
       <c r="C149" t="n">
         <v>45.97999954223633</v>
@@ -4173,7 +4173,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>51.13618850708008</v>
+        <v>51.13618469238281</v>
       </c>
       <c r="C151" t="n">
         <v>52.43999862670898</v>
@@ -4202,7 +4202,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>51.47749328613281</v>
+        <v>51.47748947143555</v>
       </c>
       <c r="C152" t="n">
         <v>52.79000091552734</v>
@@ -4260,7 +4260,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>44.10546112060547</v>
+        <v>44.10545349121094</v>
       </c>
       <c r="C154" t="n">
         <v>45.22999954223633</v>
@@ -4289,7 +4289,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>36.78216934204102</v>
+        <v>36.78217315673828</v>
       </c>
       <c r="C155" t="n">
         <v>37.72000122070312</v>
@@ -4318,7 +4318,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>37.60128784179688</v>
+        <v>37.60129165649414</v>
       </c>
       <c r="C156" t="n">
         <v>38.56000137329102</v>
@@ -4347,7 +4347,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>30.94110107421875</v>
+        <v>30.94109725952148</v>
       </c>
       <c r="C157" t="n">
         <v>31.72999954223633</v>
@@ -4376,7 +4376,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>37.26973724365234</v>
+        <v>37.26974105834961</v>
       </c>
       <c r="C158" t="n">
         <v>38.22000122070312</v>
@@ -4405,7 +4405,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>39.86360168457031</v>
+        <v>39.86361312866211</v>
       </c>
       <c r="C159" t="n">
         <v>40.88000106811523</v>
@@ -4434,7 +4434,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>40.30242919921875</v>
+        <v>40.30241775512695</v>
       </c>
       <c r="C160" t="n">
         <v>41.33000183105469</v>
@@ -4492,7 +4492,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>31.79922676086426</v>
+        <v>31.79921913146973</v>
       </c>
       <c r="C162" t="n">
         <v>32.61000061035156</v>
@@ -4521,7 +4521,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>37.63055038452148</v>
+        <v>37.63054275512695</v>
       </c>
       <c r="C163" t="n">
         <v>38.59000015258789</v>
@@ -4550,7 +4550,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>43.77390670776367</v>
+        <v>43.7739143371582</v>
       </c>
       <c r="C164" t="n">
         <v>44.88999938964844</v>
@@ -4579,7 +4579,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>44.14446640014648</v>
+        <v>44.14446258544922</v>
       </c>
       <c r="C165" t="n">
         <v>45.27000045776367</v>
@@ -4608,7 +4608,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>41.78462219238281</v>
+        <v>41.78462982177734</v>
       </c>
       <c r="C166" t="n">
         <v>42.84999847412109</v>
@@ -4637,7 +4637,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>46.36777496337891</v>
+        <v>46.36777114868164</v>
       </c>
       <c r="C167" t="n">
         <v>47.54999923706055</v>
@@ -4695,7 +4695,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>52.44287109375</v>
+        <v>52.4428825378418</v>
       </c>
       <c r="C169" t="n">
         <v>53.77999877929688</v>
@@ -4724,7 +4724,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>51.77003479003906</v>
+        <v>51.77003860473633</v>
       </c>
       <c r="C170" t="n">
         <v>53.09000015258789</v>
@@ -4811,7 +4811,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>46.69932174682617</v>
+        <v>46.69932556152344</v>
       </c>
       <c r="C173" t="n">
         <v>47.88999938964844</v>
@@ -4840,7 +4840,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>46.71881866455078</v>
+        <v>46.71882247924805</v>
       </c>
       <c r="C174" t="n">
         <v>47.90999984741211</v>
@@ -4869,7 +4869,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>50.23907089233398</v>
+        <v>50.23906326293945</v>
       </c>
       <c r="C175" t="n">
         <v>51.52000045776367</v>
@@ -4898,7 +4898,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>48.81536865234375</v>
+        <v>48.81537628173828</v>
       </c>
       <c r="C176" t="n">
         <v>50.06000137329102</v>
@@ -4927,7 +4927,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>44.37848663330078</v>
+        <v>44.37849426269531</v>
       </c>
       <c r="C177" t="n">
         <v>45.5099983215332</v>
@@ -4956,7 +4956,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>45.79244613647461</v>
+        <v>45.79244232177734</v>
       </c>
       <c r="C178" t="n">
         <v>46.95999908447266</v>
@@ -4985,7 +4985,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>49.08840942382812</v>
+        <v>49.08839797973633</v>
       </c>
       <c r="C179" t="n">
         <v>50.34000015258789</v>
@@ -5043,7 +5043,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>73.31081390380859</v>
+        <v>73.31079864501953</v>
       </c>
       <c r="C181" t="n">
         <v>75.18000030517578</v>
@@ -5072,7 +5072,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>76.32398986816406</v>
+        <v>76.323974609375</v>
       </c>
       <c r="C182" t="n">
         <v>78.26999664306641</v>
@@ -5101,7 +5101,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>89.25430297851562</v>
+        <v>89.25431060791016</v>
       </c>
       <c r="C183" t="n">
         <v>91.52999877929688</v>
@@ -5159,7 +5159,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>83.93006896972656</v>
+        <v>83.93004608154297</v>
       </c>
       <c r="C185" t="n">
         <v>86.06999969482422</v>
@@ -5188,7 +5188,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>82.04803466796875</v>
+        <v>82.04804229736328</v>
       </c>
       <c r="C186" t="n">
         <v>84.13999938964844</v>
@@ -5217,7 +5217,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>82.86717224121094</v>
+        <v>82.86715698242188</v>
       </c>
       <c r="C187" t="n">
         <v>84.98000335693359</v>
@@ -5246,7 +5246,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>75.65113830566406</v>
+        <v>75.651123046875</v>
       </c>
       <c r="C188" t="n">
         <v>77.58000183105469</v>
@@ -5275,7 +5275,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>71.86759948730469</v>
+        <v>71.86760711669922</v>
       </c>
       <c r="C189" t="n">
         <v>73.69999694824219</v>
@@ -5304,7 +5304,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>69.31198883056641</v>
+        <v>69.31199645996094</v>
       </c>
       <c r="C190" t="n">
         <v>70.98000335693359</v>
@@ -5362,7 +5362,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>82.02600860595703</v>
+        <v>82.02603149414062</v>
       </c>
       <c r="C192" t="n">
         <v>84</v>
@@ -5391,7 +5391,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>91.0579833984375</v>
+        <v>91.05796051025391</v>
       </c>
       <c r="C193" t="n">
         <v>93.15000152587891</v>
@@ -5449,7 +5449,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>86.86432647705078</v>
+        <v>86.86434173583984</v>
       </c>
       <c r="C195" t="n">
         <v>88.86000061035156</v>
@@ -5478,7 +5478,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>76.14069366455078</v>
+        <v>76.14070129394531</v>
       </c>
       <c r="C196" t="n">
         <v>77.88999938964844</v>
@@ -5507,7 +5507,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>66.7496337890625</v>
+        <v>66.74964141845703</v>
       </c>
       <c r="C197" t="n">
         <v>68.19000244140625</v>
@@ -5536,7 +5536,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>72.28028869628906</v>
+        <v>72.28028106689453</v>
       </c>
       <c r="C198" t="n">
         <v>73.83999633789062</v>
@@ -5623,7 +5623,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>55.44427871704102</v>
+        <v>55.44427490234375</v>
       </c>
       <c r="C201" t="n">
         <v>56.52999877929688</v>
@@ -5652,7 +5652,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>49.13776779174805</v>
+        <v>49.13776397705078</v>
       </c>
       <c r="C202" t="n">
         <v>50.09999847412109</v>
@@ -5681,7 +5681,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>53.17290115356445</v>
+        <v>53.17289733886719</v>
       </c>
       <c r="C203" t="n">
         <v>54.09999847412109</v>
@@ -5710,7 +5710,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>56.66206741333008</v>
+        <v>56.66206359863281</v>
       </c>
       <c r="C204" t="n">
         <v>57.65000152587891</v>
@@ -5739,7 +5739,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>49.23528671264648</v>
+        <v>49.23529052734375</v>
       </c>
       <c r="C205" t="n">
         <v>49.97999954223633</v>
@@ -5768,7 +5768,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>59.40151977539062</v>
+        <v>59.40151596069336</v>
       </c>
       <c r="C206" t="n">
         <v>60.29999923706055</v>
@@ -5797,7 +5797,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>56.95847702026367</v>
+        <v>56.95847320556641</v>
       </c>
       <c r="C207" t="n">
         <v>57.81999969482422</v>
@@ -5826,7 +5826,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>59.44092178344727</v>
+        <v>59.44092559814453</v>
       </c>
       <c r="C208" t="n">
         <v>60.34000015258789</v>
@@ -5855,7 +5855,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>63.52914810180664</v>
+        <v>63.52915954589844</v>
       </c>
       <c r="C209" t="n">
         <v>64.36000061035156</v>
@@ -5913,7 +5913,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>62.29528427124023</v>
+        <v>62.29529571533203</v>
       </c>
       <c r="C211" t="n">
         <v>63.11000061035156</v>
@@ -5994,7 +5994,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>67.27813720703125</v>
+        <v>67.27812957763672</v>
       </c>
       <c r="C214" t="n">
         <v>68.02999877929688</v>
@@ -6021,7 +6021,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>66.24127960205078</v>
+        <v>66.24128723144531</v>
       </c>
       <c r="C215" t="n">
         <v>66.87000274658203</v>
@@ -6048,7 +6048,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>75.40430450439453</v>
+        <v>75.40431976318359</v>
       </c>
       <c r="C216" t="n">
         <v>76.12000274658203</v>
@@ -6102,7 +6102,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>85.05750274658203</v>
+        <v>85.05751037597656</v>
       </c>
       <c r="C218" t="n">
         <v>85.75</v>
@@ -6156,7 +6156,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>117.0508346557617</v>
+        <v>117.0508422851562</v>
       </c>
       <c r="C220" t="n">
         <v>117.8899993896484</v>
@@ -6183,7 +6183,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>112.1559219360352</v>
+        <v>112.1559143066406</v>
       </c>
       <c r="C221" t="n">
         <v>112.9599990844727</v>
@@ -6210,7 +6210,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>124.1102294921875</v>
+        <v>124.1102142333984</v>
       </c>
       <c r="C222" t="n">
         <v>125</v>
@@ -6237,7 +6237,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>130.5937347412109</v>
+        <v>130.5937194824219</v>
       </c>
       <c r="C223" t="n">
         <v>131.5299987792969</v>
@@ -6318,7 +6318,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>103.0618286132812</v>
+        <v>103.0618362426758</v>
       </c>
       <c r="C226" t="n">
         <v>103.7099990844727</v>
@@ -6345,7 +6345,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>99.13871765136719</v>
+        <v>99.13868713378906</v>
       </c>
       <c r="C227" t="n">
         <v>99.65000152587891</v>
@@ -6461,7 +6461,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>93.27060699462891</v>
+        <v>93.27061462402344</v>
       </c>
       <c r="C231" t="n">
         <v>93.62999725341797</v>
@@ -6490,7 +6490,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>86.66917419433594</v>
+        <v>86.66918182373047</v>
       </c>
       <c r="C232" t="n">
         <v>86.88999938964844</v>
@@ -6519,7 +6519,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>76.75445556640625</v>
+        <v>76.75444030761719</v>
       </c>
       <c r="C233" t="n">
         <v>76.94999694824219</v>
@@ -6548,7 +6548,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>94.21994018554688</v>
+        <v>94.21994781494141</v>
       </c>
       <c r="C234" t="n">
         <v>94.45999908447266</v>
@@ -6577,7 +6577,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>122.9367752075195</v>
+        <v>122.9367828369141</v>
       </c>
       <c r="C235" t="n">
         <v>123.25</v>
